--- a/dist/parameters.xlsx
+++ b/dist/parameters.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G84"/>
+  <dimension ref="A1:G87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3144,6 +3144,97 @@
         </is>
       </c>
       <c r="G84" t="inlineStr">
+        <is>
+          <t>Histogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Index</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Index</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Index</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Histogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Histogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Attenuation</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Attenuation</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Attenuation</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
         <is>
           <t>Histogram</t>
         </is>
@@ -3160,7 +3251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G129"/>
+  <dimension ref="A1:G135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7593,6 +7684,200 @@
         </is>
       </c>
       <c r="G129" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Index_trab_H</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Index</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Histogram</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="G130" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Index_cort_H</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Index</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Histogram</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="G131" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>HU_trab_H</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Histogram</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="G132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>HU_cort_H</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Histogram</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="G133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Attenuation_trab_H</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Attenuation</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Histogram</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="G134" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Attenuation_cort_H</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Attenuation</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Histogram</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="G135" t="n">
         <v>0</v>
       </c>
     </row>

--- a/dist/parameters.xlsx
+++ b/dist/parameters.xlsx
@@ -474,7 +474,6 @@
           <t>Pos.Z</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>um</t>
@@ -507,8 +506,6 @@
           <t>Obj.N</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>float</t>
@@ -536,7 +533,6 @@
           <t>T.Ar</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>um^2</t>
@@ -569,7 +565,6 @@
           <t>B.Ar</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>um^2</t>
@@ -602,7 +597,6 @@
           <t>B.Ar/T.Ar</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>%</t>
@@ -635,7 +629,6 @@
           <t>T.Pm</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>um</t>
@@ -668,7 +661,6 @@
           <t>B.Pm</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>um</t>
@@ -701,7 +693,6 @@
           <t>B.Pm/B.Ar</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>1/um</t>
@@ -734,7 +725,6 @@
           <t>Av.Obj.Ar</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>um^2</t>
@@ -767,7 +757,6 @@
           <t>Av.Obj.ECDa</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>um</t>
@@ -800,7 +789,6 @@
           <t>Tb.Pf</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>1/um</t>
@@ -833,8 +821,6 @@
           <t>Eu.N</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>float</t>
@@ -862,8 +848,6 @@
           <t>Po.N(cl)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>float</t>
@@ -891,7 +875,6 @@
           <t>Po.Ar(cl)</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>um^2</t>
@@ -924,7 +907,6 @@
           <t>Po.Pm(cl)</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>um</t>
@@ -957,7 +939,6 @@
           <t>Po(cl)</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>%</t>
@@ -990,7 +971,6 @@
           <t>Po.Ar(op)</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>um^2</t>
@@ -1023,7 +1003,6 @@
           <t>Po.Ar(tot)</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>um^2</t>
@@ -1056,7 +1035,6 @@
           <t>Po(op)</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>%</t>
@@ -1089,7 +1067,6 @@
           <t>Po(tot)</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>%</t>
@@ -1122,7 +1099,6 @@
           <t>Crd.X</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>um</t>
@@ -1155,7 +1131,6 @@
           <t>Crd.Y</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>um</t>
@@ -1188,7 +1163,6 @@
           <t>MMI(x)</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t>um^4</t>
@@ -1221,7 +1195,6 @@
           <t>MMI(y)</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>um^4</t>
@@ -1254,7 +1227,6 @@
           <t>MMI(polar)</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t>um^4</t>
@@ -1287,7 +1259,6 @@
           <t>Gr.R(x)</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>um</t>
@@ -1320,7 +1291,6 @@
           <t>Gr.R(y)</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
           <t>um</t>
@@ -1353,7 +1323,6 @@
           <t>Gr.R(polar)</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
           <t>um</t>
@@ -1386,7 +1355,6 @@
           <t>Pr.In(xy)</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
           <t>um^4</t>
@@ -1419,7 +1387,6 @@
           <t>MMI(max)</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
           <t>um^4</t>
@@ -1452,7 +1419,6 @@
           <t>MMI(min)</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
           <t>um^4</t>
@@ -1485,7 +1451,6 @@
           <t>T.Or(phi)</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
           <t>°</t>
@@ -1518,8 +1483,6 @@
           <t>Ecc</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>float</t>
@@ -1547,7 +1510,6 @@
           <t>Tb.Th(pl)</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
           <t>um</t>
@@ -1580,7 +1542,6 @@
           <t>Tb.Sp(pl)</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
           <t>um</t>
@@ -1613,7 +1574,6 @@
           <t>Tb.N(pl)</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
           <t>1/um</t>
@@ -1646,8 +1606,6 @@
           <t>FD</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
           <t>float</t>
@@ -1675,7 +1633,6 @@
           <t>i.Pm</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
           <t>um</t>
@@ -1708,7 +1665,6 @@
           <t>TV</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
           <t>um^3</t>
@@ -1741,7 +1697,6 @@
           <t>BV</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
           <t>um^3</t>
@@ -1774,7 +1729,6 @@
           <t>BV/TV</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
           <t>%</t>
@@ -1807,7 +1761,6 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
           <t>um^2</t>
@@ -1840,7 +1793,6 @@
           <t>BS</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
           <t>um^2</t>
@@ -1873,7 +1825,6 @@
           <t>i.S</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
           <t>um^2</t>
@@ -1906,7 +1857,6 @@
           <t>BS/BV</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
           <t>1/um</t>
@@ -1939,7 +1889,6 @@
           <t>BS/TV</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
           <t>1/um</t>
@@ -1972,7 +1921,6 @@
           <t>Tb.Th</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
           <t>um</t>
@@ -2005,7 +1953,6 @@
           <t>Tb.Sp</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
           <t>um</t>
@@ -2038,7 +1985,6 @@
           <t>Tb.N</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
           <t>1/um</t>
@@ -2071,7 +2017,6 @@
           <t>Tb.Pf</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
           <t>1/um</t>
@@ -2104,7 +2049,6 @@
           <t>Crd.X</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
           <t>um</t>
@@ -2137,7 +2081,6 @@
           <t>Crd.Y</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
           <t>um</t>
@@ -2170,7 +2113,6 @@
           <t>Crd.Z</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
           <t>um</t>
@@ -2203,8 +2145,6 @@
           <t>SMI</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>float</t>
@@ -2232,8 +2172,6 @@
           <t>DA</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
           <t>float</t>
@@ -2266,7 +2204,6 @@
           <t>Degree of anisotropy (math)</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
           <t>float</t>
@@ -2294,8 +2231,6 @@
           <t>FD</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>float</t>
@@ -2323,8 +2258,6 @@
           <t>Obj.N</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
           <t>float</t>
@@ -2352,8 +2285,6 @@
           <t>Po.N(cl)</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
           <t>float</t>
@@ -2381,7 +2312,6 @@
           <t>Po.V(cl)</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
           <t>um^3</t>
@@ -2414,7 +2344,6 @@
           <t>Po.S(cl)</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
           <t>um^2</t>
@@ -2447,7 +2376,6 @@
           <t>Po.V(op)</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
           <t>um^3</t>
@@ -2480,7 +2408,6 @@
           <t>Po(op)</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
           <t>%</t>
@@ -2513,7 +2440,6 @@
           <t>Po.V(tot)</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
           <t>um^3</t>
@@ -2546,7 +2472,6 @@
           <t>Po(cl)</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
           <t>%</t>
@@ -2579,7 +2504,6 @@
           <t>Po(tot)</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
           <t>%</t>
@@ -2612,8 +2536,6 @@
           <t>Eu.N</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
           <t>float</t>
@@ -2641,8 +2563,6 @@
           <t>Conn</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
           <t>float</t>
@@ -2670,7 +2590,6 @@
           <t>Conn.Dn</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
           <t>1/um^3</t>
@@ -2703,7 +2622,6 @@
           <t>SD(Tb.Th)</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
           <t>um</t>
@@ -2736,7 +2654,6 @@
           <t>SD(Tb.Sp)</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
           <t>um</t>
@@ -2769,7 +2686,6 @@
           <t>MMI(x)</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
           <t>um^5</t>
@@ -2802,7 +2718,6 @@
           <t>MMI(y)</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
           <t>um^5</t>
@@ -2835,7 +2750,6 @@
           <t>MMI(z)</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
           <t>um^5</t>
@@ -2868,7 +2782,6 @@
           <t>MMI(polar)</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
           <t>um^5</t>
@@ -2901,7 +2814,6 @@
           <t>Gr.R(x)</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
           <t>um</t>
@@ -2934,7 +2846,6 @@
           <t>Gr.R(y)</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
           <t>um</t>
@@ -2967,7 +2878,6 @@
           <t>Gr.R(z)</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
           <t>um</t>
@@ -3000,7 +2910,6 @@
           <t>Gr.R(polar)</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
           <t>um</t>
@@ -3033,7 +2942,6 @@
           <t>Pr.In(xy)</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
           <t>um^5</t>
@@ -3066,7 +2974,6 @@
           <t>Pr.In(xz)</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
           <t>um^5</t>
@@ -3099,7 +3006,6 @@
           <t>Pr.In(yz)</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
           <t>um^5</t>
@@ -3132,7 +3038,6 @@
           <t>BMD</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
           <t>g/cm3</t>
@@ -3165,8 +3070,6 @@
           <t>Index</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
           <t>float</t>
@@ -3194,7 +3097,6 @@
           <t>HU</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
           <t>HU</t>
@@ -3227,8 +3129,6 @@
           <t>Attenuation</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
           <t>float</t>
@@ -3832,7 +3732,6 @@
           <t>3D</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>float</t>
@@ -3863,7 +3762,6 @@
           <t>3D</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>float</t>
@@ -3894,7 +3792,6 @@
           <t>3D</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>float</t>
@@ -3925,7 +3822,6 @@
           <t>3D</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>float</t>
@@ -3956,7 +3852,6 @@
           <t>3D</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>float</t>
@@ -3987,7 +3882,6 @@
           <t>3D</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>float</t>
@@ -4263,7 +4157,6 @@
           <t>3D</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
           <t>float</t>
@@ -4294,7 +4187,6 @@
           <t>3D</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
           <t>float</t>
@@ -5340,7 +5232,6 @@
           <t>3D</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
           <t>float</t>
@@ -5371,7 +5262,6 @@
           <t>3D</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
           <t>float</t>
@@ -5402,7 +5292,6 @@
           <t>3D</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
           <t>float</t>
@@ -5433,7 +5322,6 @@
           <t>3D</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
           <t>float</t>
@@ -5464,7 +5352,6 @@
           <t>3D</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
           <t>float</t>
@@ -5495,7 +5382,6 @@
           <t>3D</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
           <t>float</t>
@@ -5771,7 +5657,6 @@
           <t>3D</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
           <t>float</t>
@@ -5802,7 +5687,6 @@
           <t>3D</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
           <t>float</t>
@@ -6358,7 +6242,6 @@
           <t>2D</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
           <t>float</t>
@@ -6704,7 +6587,6 @@
           <t>2D</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
           <t>float</t>
@@ -6735,7 +6617,6 @@
           <t>2D</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
           <t>float</t>
@@ -7431,7 +7312,6 @@
           <t>2D</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr">
         <is>
           <t>float</t>
@@ -7567,7 +7447,6 @@
           <t>2D</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr">
         <is>
           <t>float</t>
@@ -7703,7 +7582,6 @@
           <t>Histogram</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
           <t>float</t>
@@ -7734,7 +7612,6 @@
           <t>Histogram</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
           <t>float</t>
@@ -7835,7 +7712,6 @@
           <t>Histogram</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
           <t>float</t>
@@ -7866,7 +7742,6 @@
           <t>Histogram</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
           <t>float</t>
@@ -7987,7 +7862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8810,6 +8685,526 @@
       </c>
       <c r="D41" t="n">
         <v>18</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>标准模板（长骨专用）区分松质骨皮质骨参数_副本</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>DATE_META</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>标准模板（长骨专用）区分松质骨皮质骨参数_副本</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>样品ID</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>SAMPLE_ID_META</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>标准模板（长骨专用）区分松质骨皮质骨参数_副本</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>BMD (g/cm3)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>BMD_trab_H</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>标准模板（长骨专用）区分松质骨皮质骨参数_副本</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>TV (um^3)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>TV_trab_3D</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>标准模板（长骨专用）区分松质骨皮质骨参数_副本</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>BV (um^3)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>BV_trab_3D</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>标准模板（长骨专用）区分松质骨皮质骨参数_副本</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>BV/TV (%)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>BVTV_trab_3D</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>标准模板（长骨专用）区分松质骨皮质骨参数_副本</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>BS/BV (1/um)</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>BSBV_trab_3D</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>标准模板（长骨专用）区分松质骨皮质骨参数_副本</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Tb.Th (um)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>TbTh_trab_3D</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>标准模板（长骨专用）区分松质骨皮质骨参数_副本</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Tb.Sp (um)</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>TbSp_trab_3D</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>标准模板（长骨专用）区分松质骨皮质骨参数_副本</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Tb.N (1/um)</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>TbN_trab_3D</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>标准模板（长骨专用）区分松质骨皮质骨参数_副本</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>DA_trab_3D</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>标准模板（长骨专用）区分松质骨皮质骨参数_副本</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>DA(math)</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>DA_ratio_trab_3D</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>标准模板（长骨专用）区分松质骨皮质骨参数_副本</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>BMD (g/cm3)</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>BMD_cort_H</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>标准模板（长骨专用）区分松质骨皮质骨参数_副本</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>BV/TV (%)</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>BVTV_cort_3D</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>标准模板（长骨专用）区分松质骨皮质骨参数_副本</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>BS/BV (1/um)</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>BSBV_cort_3D</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>标准模板（长骨专用）区分松质骨皮质骨参数_副本</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Tb.Th (um)</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>TbTh_cort_3D</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>标准模板（长骨专用）区分松质骨皮质骨参数_副本</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Po(cl) (%)</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Po_cl_cort_3D</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>标准模板（长骨专用）区分松质骨皮质骨参数_副本</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Po(tot) (%)</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Po_tot_cort_3D</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>标准模板（长骨专用）区分松质骨皮质骨参数_副本</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>T.Ar (um^2)</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>TAr_cort_2D</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>标准模板（长骨专用）区分松质骨皮质骨参数_副本</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>BAr_calc</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>BAr_calc</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>标准模板（长骨专用）区分松质骨皮质骨参数_副本</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>B.Ar (um^2)</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>BAr_cort_2D</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>标准模板（长骨专用）区分松质骨皮质骨参数_副本</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>BArRatio_calc</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>BArRatio_calc</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>标准模板（长骨专用）区分松质骨皮质骨参数_副本</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>T.Pm (um)</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>TPm_cort_2D</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>标准模板（长骨专用）区分松质骨皮质骨参数_副本</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>B.Pm (um)</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>BPm_cort_2D</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>标准模板（长骨专用）区分松质骨皮质骨参数_副本</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>DA_cort_3D</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>标准模板（长骨专用）区分松质骨皮质骨参数_副本</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>DA(math)</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>DA_ratio_cort_3D</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/dist/parameters.xlsx
+++ b/dist/parameters.xlsx
@@ -474,6 +474,7 @@
           <t>Pos.Z</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>um</t>
@@ -506,6 +507,8 @@
           <t>Obj.N</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>float</t>
@@ -533,6 +536,7 @@
           <t>T.Ar</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>um^2</t>
@@ -565,6 +569,7 @@
           <t>B.Ar</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>um^2</t>
@@ -597,6 +602,7 @@
           <t>B.Ar/T.Ar</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>%</t>
@@ -629,6 +635,7 @@
           <t>T.Pm</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>um</t>
@@ -661,6 +668,7 @@
           <t>B.Pm</t>
         </is>
       </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>um</t>
@@ -693,6 +701,7 @@
           <t>B.Pm/B.Ar</t>
         </is>
       </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>1/um</t>
@@ -725,6 +734,7 @@
           <t>Av.Obj.Ar</t>
         </is>
       </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>um^2</t>
@@ -757,6 +767,7 @@
           <t>Av.Obj.ECDa</t>
         </is>
       </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>um</t>
@@ -789,6 +800,7 @@
           <t>Tb.Pf</t>
         </is>
       </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>1/um</t>
@@ -821,6 +833,8 @@
           <t>Eu.N</t>
         </is>
       </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>float</t>
@@ -848,6 +862,8 @@
           <t>Po.N(cl)</t>
         </is>
       </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>float</t>
@@ -875,6 +891,7 @@
           <t>Po.Ar(cl)</t>
         </is>
       </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>um^2</t>
@@ -907,6 +924,7 @@
           <t>Po.Pm(cl)</t>
         </is>
       </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>um</t>
@@ -939,6 +957,7 @@
           <t>Po(cl)</t>
         </is>
       </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>%</t>
@@ -971,6 +990,7 @@
           <t>Po.Ar(op)</t>
         </is>
       </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>um^2</t>
@@ -1003,6 +1023,7 @@
           <t>Po.Ar(tot)</t>
         </is>
       </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>um^2</t>
@@ -1035,6 +1056,7 @@
           <t>Po(op)</t>
         </is>
       </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>%</t>
@@ -1067,6 +1089,7 @@
           <t>Po(tot)</t>
         </is>
       </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>%</t>
@@ -1099,6 +1122,7 @@
           <t>Crd.X</t>
         </is>
       </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>um</t>
@@ -1131,6 +1155,7 @@
           <t>Crd.Y</t>
         </is>
       </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>um</t>
@@ -1163,6 +1188,7 @@
           <t>MMI(x)</t>
         </is>
       </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t>um^4</t>
@@ -1195,6 +1221,7 @@
           <t>MMI(y)</t>
         </is>
       </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>um^4</t>
@@ -1227,6 +1254,7 @@
           <t>MMI(polar)</t>
         </is>
       </c>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t>um^4</t>
@@ -1259,6 +1287,7 @@
           <t>Gr.R(x)</t>
         </is>
       </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>um</t>
@@ -1291,6 +1320,7 @@
           <t>Gr.R(y)</t>
         </is>
       </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
           <t>um</t>
@@ -1323,6 +1353,7 @@
           <t>Gr.R(polar)</t>
         </is>
       </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
           <t>um</t>
@@ -1355,6 +1386,7 @@
           <t>Pr.In(xy)</t>
         </is>
       </c>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
           <t>um^4</t>
@@ -1387,6 +1419,7 @@
           <t>MMI(max)</t>
         </is>
       </c>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
           <t>um^4</t>
@@ -1419,6 +1452,7 @@
           <t>MMI(min)</t>
         </is>
       </c>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
           <t>um^4</t>
@@ -1451,6 +1485,7 @@
           <t>T.Or(phi)</t>
         </is>
       </c>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
           <t>°</t>
@@ -1483,6 +1518,8 @@
           <t>Ecc</t>
         </is>
       </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>float</t>
@@ -1510,6 +1547,7 @@
           <t>Tb.Th(pl)</t>
         </is>
       </c>
+      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
           <t>um</t>
@@ -1542,6 +1580,7 @@
           <t>Tb.Sp(pl)</t>
         </is>
       </c>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
           <t>um</t>
@@ -1574,6 +1613,7 @@
           <t>Tb.N(pl)</t>
         </is>
       </c>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
           <t>1/um</t>
@@ -1606,6 +1646,8 @@
           <t>FD</t>
         </is>
       </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
           <t>float</t>
@@ -1633,6 +1675,7 @@
           <t>i.Pm</t>
         </is>
       </c>
+      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
           <t>um</t>
@@ -1665,6 +1708,7 @@
           <t>TV</t>
         </is>
       </c>
+      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
           <t>um^3</t>
@@ -1697,6 +1741,7 @@
           <t>BV</t>
         </is>
       </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
           <t>um^3</t>
@@ -1729,6 +1774,7 @@
           <t>BV/TV</t>
         </is>
       </c>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
           <t>%</t>
@@ -1761,6 +1807,7 @@
           <t>TS</t>
         </is>
       </c>
+      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
           <t>um^2</t>
@@ -1793,6 +1840,7 @@
           <t>BS</t>
         </is>
       </c>
+      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
           <t>um^2</t>
@@ -1825,6 +1873,7 @@
           <t>i.S</t>
         </is>
       </c>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
           <t>um^2</t>
@@ -1857,6 +1906,7 @@
           <t>BS/BV</t>
         </is>
       </c>
+      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
           <t>1/um</t>
@@ -1889,6 +1939,7 @@
           <t>BS/TV</t>
         </is>
       </c>
+      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
           <t>1/um</t>
@@ -1921,6 +1972,7 @@
           <t>Tb.Th</t>
         </is>
       </c>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
           <t>um</t>
@@ -1953,6 +2005,7 @@
           <t>Tb.Sp</t>
         </is>
       </c>
+      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
           <t>um</t>
@@ -1985,6 +2038,7 @@
           <t>Tb.N</t>
         </is>
       </c>
+      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
           <t>1/um</t>
@@ -2017,6 +2071,7 @@
           <t>Tb.Pf</t>
         </is>
       </c>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
           <t>1/um</t>
@@ -2049,6 +2104,7 @@
           <t>Crd.X</t>
         </is>
       </c>
+      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
           <t>um</t>
@@ -2081,6 +2137,7 @@
           <t>Crd.Y</t>
         </is>
       </c>
+      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
           <t>um</t>
@@ -2113,6 +2170,7 @@
           <t>Crd.Z</t>
         </is>
       </c>
+      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
           <t>um</t>
@@ -2145,6 +2203,8 @@
           <t>SMI</t>
         </is>
       </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>float</t>
@@ -2172,6 +2232,8 @@
           <t>DA</t>
         </is>
       </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
           <t>float</t>
@@ -2204,6 +2266,7 @@
           <t>Degree of anisotropy (math)</t>
         </is>
       </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
           <t>float</t>
@@ -2231,6 +2294,8 @@
           <t>FD</t>
         </is>
       </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>float</t>
@@ -2258,6 +2323,8 @@
           <t>Obj.N</t>
         </is>
       </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
           <t>float</t>
@@ -2285,6 +2352,8 @@
           <t>Po.N(cl)</t>
         </is>
       </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
           <t>float</t>
@@ -2312,6 +2381,7 @@
           <t>Po.V(cl)</t>
         </is>
       </c>
+      <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
           <t>um^3</t>
@@ -2344,6 +2414,7 @@
           <t>Po.S(cl)</t>
         </is>
       </c>
+      <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
           <t>um^2</t>
@@ -2376,6 +2447,7 @@
           <t>Po.V(op)</t>
         </is>
       </c>
+      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
           <t>um^3</t>
@@ -2408,6 +2480,7 @@
           <t>Po(op)</t>
         </is>
       </c>
+      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
           <t>%</t>
@@ -2440,6 +2513,7 @@
           <t>Po.V(tot)</t>
         </is>
       </c>
+      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
           <t>um^3</t>
@@ -2472,6 +2546,7 @@
           <t>Po(cl)</t>
         </is>
       </c>
+      <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
           <t>%</t>
@@ -2504,6 +2579,7 @@
           <t>Po(tot)</t>
         </is>
       </c>
+      <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
           <t>%</t>
@@ -2536,6 +2612,8 @@
           <t>Eu.N</t>
         </is>
       </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
           <t>float</t>
@@ -2563,6 +2641,8 @@
           <t>Conn</t>
         </is>
       </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
           <t>float</t>
@@ -2590,6 +2670,7 @@
           <t>Conn.Dn</t>
         </is>
       </c>
+      <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
           <t>1/um^3</t>
@@ -2622,6 +2703,7 @@
           <t>SD(Tb.Th)</t>
         </is>
       </c>
+      <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
           <t>um</t>
@@ -2654,6 +2736,7 @@
           <t>SD(Tb.Sp)</t>
         </is>
       </c>
+      <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
           <t>um</t>
@@ -2686,6 +2769,7 @@
           <t>MMI(x)</t>
         </is>
       </c>
+      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
           <t>um^5</t>
@@ -2718,6 +2802,7 @@
           <t>MMI(y)</t>
         </is>
       </c>
+      <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
           <t>um^5</t>
@@ -2750,6 +2835,7 @@
           <t>MMI(z)</t>
         </is>
       </c>
+      <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
           <t>um^5</t>
@@ -2782,6 +2868,7 @@
           <t>MMI(polar)</t>
         </is>
       </c>
+      <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
           <t>um^5</t>
@@ -2814,6 +2901,7 @@
           <t>Gr.R(x)</t>
         </is>
       </c>
+      <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
           <t>um</t>
@@ -2846,6 +2934,7 @@
           <t>Gr.R(y)</t>
         </is>
       </c>
+      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
           <t>um</t>
@@ -2878,6 +2967,7 @@
           <t>Gr.R(z)</t>
         </is>
       </c>
+      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
           <t>um</t>
@@ -2910,6 +3000,7 @@
           <t>Gr.R(polar)</t>
         </is>
       </c>
+      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
           <t>um</t>
@@ -2942,6 +3033,7 @@
           <t>Pr.In(xy)</t>
         </is>
       </c>
+      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
           <t>um^5</t>
@@ -2974,6 +3066,7 @@
           <t>Pr.In(xz)</t>
         </is>
       </c>
+      <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
           <t>um^5</t>
@@ -3006,6 +3099,7 @@
           <t>Pr.In(yz)</t>
         </is>
       </c>
+      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
           <t>um^5</t>
@@ -3038,6 +3132,7 @@
           <t>BMD</t>
         </is>
       </c>
+      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
           <t>g/cm3</t>
@@ -3070,6 +3165,8 @@
           <t>Index</t>
         </is>
       </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
           <t>float</t>
@@ -3097,6 +3194,7 @@
           <t>HU</t>
         </is>
       </c>
+      <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
           <t>HU</t>
@@ -3129,6 +3227,8 @@
           <t>Attenuation</t>
         </is>
       </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
           <t>float</t>
@@ -3732,6 +3832,7 @@
           <t>3D</t>
         </is>
       </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>float</t>
@@ -3762,6 +3863,7 @@
           <t>3D</t>
         </is>
       </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>float</t>
@@ -3792,6 +3894,7 @@
           <t>3D</t>
         </is>
       </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>float</t>
@@ -3822,6 +3925,7 @@
           <t>3D</t>
         </is>
       </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>float</t>
@@ -3852,6 +3956,7 @@
           <t>3D</t>
         </is>
       </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>float</t>
@@ -3882,6 +3987,7 @@
           <t>3D</t>
         </is>
       </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>float</t>
@@ -4157,6 +4263,7 @@
           <t>3D</t>
         </is>
       </c>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
           <t>float</t>
@@ -4187,6 +4294,7 @@
           <t>3D</t>
         </is>
       </c>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
           <t>float</t>
@@ -5232,6 +5340,7 @@
           <t>3D</t>
         </is>
       </c>
+      <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
           <t>float</t>
@@ -5262,6 +5371,7 @@
           <t>3D</t>
         </is>
       </c>
+      <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
           <t>float</t>
@@ -5292,6 +5402,7 @@
           <t>3D</t>
         </is>
       </c>
+      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
           <t>float</t>
@@ -5322,6 +5433,7 @@
           <t>3D</t>
         </is>
       </c>
+      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
           <t>float</t>
@@ -5352,6 +5464,7 @@
           <t>3D</t>
         </is>
       </c>
+      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
           <t>float</t>
@@ -5382,6 +5495,7 @@
           <t>3D</t>
         </is>
       </c>
+      <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
           <t>float</t>
@@ -5657,6 +5771,7 @@
           <t>3D</t>
         </is>
       </c>
+      <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
           <t>float</t>
@@ -5687,6 +5802,7 @@
           <t>3D</t>
         </is>
       </c>
+      <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
           <t>float</t>
@@ -6242,6 +6358,7 @@
           <t>2D</t>
         </is>
       </c>
+      <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
           <t>float</t>
@@ -6587,6 +6704,7 @@
           <t>2D</t>
         </is>
       </c>
+      <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
           <t>float</t>
@@ -6617,6 +6735,7 @@
           <t>2D</t>
         </is>
       </c>
+      <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
           <t>float</t>
@@ -7312,6 +7431,7 @@
           <t>2D</t>
         </is>
       </c>
+      <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr">
         <is>
           <t>float</t>
@@ -7447,6 +7567,7 @@
           <t>2D</t>
         </is>
       </c>
+      <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr">
         <is>
           <t>float</t>
@@ -7582,6 +7703,7 @@
           <t>Histogram</t>
         </is>
       </c>
+      <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
           <t>float</t>
@@ -7612,6 +7734,7 @@
           <t>Histogram</t>
         </is>
       </c>
+      <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
           <t>float</t>
@@ -7712,6 +7835,7 @@
           <t>Histogram</t>
         </is>
       </c>
+      <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
           <t>float</t>
@@ -7742,6 +7866,7 @@
           <t>Histogram</t>
         </is>
       </c>
+      <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
           <t>float</t>
@@ -7862,7 +7987,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D67"/>
+  <dimension ref="A1:D59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8330,7 +8455,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>通用模板（直接提取参数）</t>
+          <t>通用模板（同一样品CSV内多ROI分析结果）</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -8350,7 +8475,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>通用模板（直接提取参数）</t>
+          <t>通用模板（同一样品CSV内多ROI分析结果）</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -8370,7 +8495,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>通用模板（直接提取参数）</t>
+          <t>通用模板（同一样品CSV内多ROI分析结果）</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -8390,7 +8515,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>通用模板（直接提取参数）</t>
+          <t>通用模板（同一样品CSV内多ROI分析结果）</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -8410,7 +8535,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>通用模板（直接提取参数）</t>
+          <t>通用模板（同一样品CSV内多ROI分析结果）</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -8430,7 +8555,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>通用模板（直接提取参数）</t>
+          <t>通用模板（同一样品CSV内多ROI分析结果）</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -8450,7 +8575,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>通用模板（直接提取参数）</t>
+          <t>通用模板（同一样品CSV内多ROI分析结果）</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -8470,7 +8595,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>通用模板（直接提取参数）</t>
+          <t>通用模板（同一样品CSV内多ROI分析结果）</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -8490,7 +8615,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>通用模板（直接提取参数）</t>
+          <t>通用模板（同一样品CSV内多ROI分析结果）</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -8510,7 +8635,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>通用模板（直接提取参数）</t>
+          <t>通用模板（同一样品CSV内多ROI分析结果）</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -8530,7 +8655,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>通用模板（直接提取参数）</t>
+          <t>通用模板（同一样品CSV内多ROI分析结果）</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -8550,7 +8675,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>通用模板（直接提取参数）</t>
+          <t>通用模板（同一样品CSV内多ROI分析结果）</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -8570,7 +8695,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>通用模板（直接提取参数）</t>
+          <t>通用模板（同一样品CSV内多ROI分析结果）</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -8590,7 +8715,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>通用模板（直接提取参数）</t>
+          <t>通用模板（同一样品CSV内多ROI分析结果）</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -8610,7 +8735,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>通用模板（直接提取参数）</t>
+          <t>通用模板（同一样品CSV内多ROI分析结果）</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -8630,7 +8755,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>通用模板（直接提取参数）</t>
+          <t>通用模板（同一样品CSV内多ROI分析结果）</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -8650,7 +8775,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>通用模板（直接提取参数）</t>
+          <t>通用模板（同一样品CSV内多ROI分析结果）</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -8670,7 +8795,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>通用模板（直接提取参数）</t>
+          <t>通用模板（同一样品CSV内多ROI分析结果）</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -8690,7 +8815,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>标准模板（长骨专用）区分松质骨皮质骨参数_副本</t>
+          <t>通用模板（同一样品不同VOI数据结果）</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -8710,7 +8835,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>标准模板（长骨专用）区分松质骨皮质骨参数_副本</t>
+          <t>通用模板（同一样品不同VOI数据结果）</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -8730,7 +8855,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>标准模板（长骨专用）区分松质骨皮质骨参数_副本</t>
+          <t>通用模板（同一样品不同VOI数据结果）</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -8750,12 +8875,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>标准模板（长骨专用）区分松质骨皮质骨参数_副本</t>
+          <t>通用模板（同一样品不同VOI数据结果）</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>TV (um^3)</t>
+          <t>TV(um3)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -8770,12 +8895,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>标准模板（长骨专用）区分松质骨皮质骨参数_副本</t>
+          <t>通用模板（同一样品不同VOI数据结果）</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BV (um^3)</t>
+          <t>BV(um3)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -8790,12 +8915,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>标准模板（长骨专用）区分松质骨皮质骨参数_副本</t>
+          <t>通用模板（同一样品不同VOI数据结果）</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BV/TV (%)</t>
+          <t>BV/TV(%)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -8810,7 +8935,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>标准模板（长骨专用）区分松质骨皮质骨参数_副本</t>
+          <t>通用模板（同一样品不同VOI数据结果）</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -8830,7 +8955,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>标准模板（长骨专用）区分松质骨皮质骨参数_副本</t>
+          <t>通用模板（同一样品不同VOI数据结果）</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -8850,7 +8975,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>标准模板（长骨专用）区分松质骨皮质骨参数_副本</t>
+          <t>通用模板（同一样品不同VOI数据结果）</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -8870,7 +8995,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>标准模板（长骨专用）区分松质骨皮质骨参数_副本</t>
+          <t>通用模板（同一样品不同VOI数据结果）</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -8890,17 +9015,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>标准模板（长骨专用）区分松质骨皮质骨参数_副本</t>
+          <t>通用模板（同一样品不同VOI数据结果）</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>DA</t>
+          <t>Po.N(cl)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>DA_trab_3D</t>
+          <t>PoNcl3D_trab_3D</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -8910,17 +9035,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>标准模板（长骨专用）区分松质骨皮质骨参数_副本</t>
+          <t>通用模板（同一样品不同VOI数据结果）</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>DA(math)</t>
+          <t>Po.V(cl)(um3)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>DA_ratio_trab_3D</t>
+          <t>PoVcl_trab_3D</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -8930,17 +9055,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>标准模板（长骨专用）区分松质骨皮质骨参数_副本</t>
+          <t>通用模板（同一样品不同VOI数据结果）</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>BMD (g/cm3)</t>
+          <t>Po.S(cl)(um2)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>BMD_cort_H</t>
+          <t>PoScl_trab_3D</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -8950,17 +9075,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>标准模板（长骨专用）区分松质骨皮质骨参数_副本</t>
+          <t>通用模板（同一样品不同VOI数据结果）</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BV/TV (%)</t>
+          <t>Po(cl)(%)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>BVTV_cort_3D</t>
+          <t>Po_cl_trab_3D</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -8970,17 +9095,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>标准模板（长骨专用）区分松质骨皮质骨参数_副本</t>
+          <t>通用模板（同一样品不同VOI数据结果）</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>BS/BV (1/um)</t>
+          <t>Po.V(op)(um3)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>BSBV_cort_3D</t>
+          <t>PoVop_trab_3D</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -8990,17 +9115,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>标准模板（长骨专用）区分松质骨皮质骨参数_副本</t>
+          <t>通用模板（同一样品不同VOI数据结果）</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Tb.Th (um)</t>
+          <t>Po(op)(%)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>TbTh_cort_3D</t>
+          <t>Po_op3D_trab_3D</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -9010,17 +9135,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>标准模板（长骨专用）区分松质骨皮质骨参数_副本</t>
+          <t>通用模板（同一样品不同VOI数据结果）</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Po(cl) (%)</t>
+          <t>Po.V(tot)(um3)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Po_cl_cort_3D</t>
+          <t>PoVtot_trab_3D</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -9030,181 +9155,21 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>标准模板（长骨专用）区分松质骨皮质骨参数_副本</t>
+          <t>通用模板（同一样品不同VOI数据结果）</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Po(tot) (%)</t>
+          <t>Po(tot)(%)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Po_tot_cort_3D</t>
+          <t>Po_tot_trab_3D</t>
         </is>
       </c>
       <c r="D59" t="n">
         <v>18</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>标准模板（长骨专用）区分松质骨皮质骨参数_副本</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>T.Ar (um^2)</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>TAr_cort_2D</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>标准模板（长骨专用）区分松质骨皮质骨参数_副本</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>BAr_calc</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>BAr_calc</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>标准模板（长骨专用）区分松质骨皮质骨参数_副本</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>B.Ar (um^2)</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>BAr_cort_2D</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>标准模板（长骨专用）区分松质骨皮质骨参数_副本</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>BArRatio_calc</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>BArRatio_calc</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>标准模板（长骨专用）区分松质骨皮质骨参数_副本</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>T.Pm (um)</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>TPm_cort_2D</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>标准模板（长骨专用）区分松质骨皮质骨参数_副本</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>B.Pm (um)</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>BPm_cort_2D</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>标准模板（长骨专用）区分松质骨皮质骨参数_副本</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>DA</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>DA_cort_3D</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>标准模板（长骨专用）区分松质骨皮质骨参数_副本</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>DA(math)</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>DA_ratio_cort_3D</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -9218,7 +9183,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9248,10 +9213,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>样品ID规则</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>{parent}_{file_prefix}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>日期提取方式</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>csv_header</t>
         </is>

--- a/dist/parameters.xlsx
+++ b/dist/parameters.xlsx
@@ -7987,7 +7987,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D59"/>
+  <dimension ref="A1:E59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8011,6 +8011,11 @@
           <t>顺序</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>样品ID规则</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -8031,6 +8036,7 @@
       <c r="D2" t="n">
         <v>1</v>
       </c>
+      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8051,6 +8057,7 @@
       <c r="D3" t="n">
         <v>2</v>
       </c>
+      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8071,6 +8078,7 @@
       <c r="D4" t="n">
         <v>3</v>
       </c>
+      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8091,6 +8099,7 @@
       <c r="D5" t="n">
         <v>4</v>
       </c>
+      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8111,6 +8120,7 @@
       <c r="D6" t="n">
         <v>5</v>
       </c>
+      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8131,6 +8141,7 @@
       <c r="D7" t="n">
         <v>6</v>
       </c>
+      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8151,6 +8162,7 @@
       <c r="D8" t="n">
         <v>7</v>
       </c>
+      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8171,6 +8183,7 @@
       <c r="D9" t="n">
         <v>8</v>
       </c>
+      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8191,6 +8204,7 @@
       <c r="D10" t="n">
         <v>9</v>
       </c>
+      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -8211,6 +8225,7 @@
       <c r="D11" t="n">
         <v>10</v>
       </c>
+      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -8231,6 +8246,7 @@
       <c r="D12" t="n">
         <v>11</v>
       </c>
+      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -8251,6 +8267,7 @@
       <c r="D13" t="n">
         <v>12</v>
       </c>
+      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -8271,6 +8288,7 @@
       <c r="D14" t="n">
         <v>13</v>
       </c>
+      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -8291,6 +8309,7 @@
       <c r="D15" t="n">
         <v>14</v>
       </c>
+      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -8311,6 +8330,7 @@
       <c r="D16" t="n">
         <v>15</v>
       </c>
+      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -8331,6 +8351,7 @@
       <c r="D17" t="n">
         <v>16</v>
       </c>
+      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -8351,6 +8372,7 @@
       <c r="D18" t="n">
         <v>17</v>
       </c>
+      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -8371,6 +8393,7 @@
       <c r="D19" t="n">
         <v>18</v>
       </c>
+      <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -8391,6 +8414,7 @@
       <c r="D20" t="n">
         <v>19</v>
       </c>
+      <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -8411,6 +8435,7 @@
       <c r="D21" t="n">
         <v>20</v>
       </c>
+      <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -8431,6 +8456,7 @@
       <c r="D22" t="n">
         <v>21</v>
       </c>
+      <c r="E22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -8451,6 +8477,7 @@
       <c r="D23" t="n">
         <v>22</v>
       </c>
+      <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -8471,6 +8498,7 @@
       <c r="D24" t="n">
         <v>1</v>
       </c>
+      <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -8491,6 +8519,7 @@
       <c r="D25" t="n">
         <v>2</v>
       </c>
+      <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -8511,6 +8540,7 @@
       <c r="D26" t="n">
         <v>3</v>
       </c>
+      <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -8531,6 +8561,7 @@
       <c r="D27" t="n">
         <v>4</v>
       </c>
+      <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -8551,6 +8582,7 @@
       <c r="D28" t="n">
         <v>5</v>
       </c>
+      <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -8571,6 +8603,7 @@
       <c r="D29" t="n">
         <v>6</v>
       </c>
+      <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -8591,6 +8624,7 @@
       <c r="D30" t="n">
         <v>7</v>
       </c>
+      <c r="E30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -8611,6 +8645,7 @@
       <c r="D31" t="n">
         <v>8</v>
       </c>
+      <c r="E31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -8631,6 +8666,7 @@
       <c r="D32" t="n">
         <v>9</v>
       </c>
+      <c r="E32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -8651,6 +8687,7 @@
       <c r="D33" t="n">
         <v>10</v>
       </c>
+      <c r="E33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -8671,6 +8708,7 @@
       <c r="D34" t="n">
         <v>11</v>
       </c>
+      <c r="E34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -8691,6 +8729,7 @@
       <c r="D35" t="n">
         <v>12</v>
       </c>
+      <c r="E35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -8711,6 +8750,7 @@
       <c r="D36" t="n">
         <v>13</v>
       </c>
+      <c r="E36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -8731,6 +8771,7 @@
       <c r="D37" t="n">
         <v>14</v>
       </c>
+      <c r="E37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -8751,6 +8792,7 @@
       <c r="D38" t="n">
         <v>15</v>
       </c>
+      <c r="E38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -8771,6 +8813,7 @@
       <c r="D39" t="n">
         <v>16</v>
       </c>
+      <c r="E39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -8791,6 +8834,7 @@
       <c r="D40" t="n">
         <v>17</v>
       </c>
+      <c r="E40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -8811,6 +8855,7 @@
       <c r="D41" t="n">
         <v>18</v>
       </c>
+      <c r="E41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -8831,6 +8876,7 @@
       <c r="D42" t="n">
         <v>1</v>
       </c>
+      <c r="E42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -8851,6 +8897,7 @@
       <c r="D43" t="n">
         <v>2</v>
       </c>
+      <c r="E43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -8871,6 +8918,7 @@
       <c r="D44" t="n">
         <v>3</v>
       </c>
+      <c r="E44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -8891,6 +8939,7 @@
       <c r="D45" t="n">
         <v>4</v>
       </c>
+      <c r="E45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -8911,6 +8960,7 @@
       <c r="D46" t="n">
         <v>5</v>
       </c>
+      <c r="E46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -8931,6 +8981,7 @@
       <c r="D47" t="n">
         <v>6</v>
       </c>
+      <c r="E47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -8951,6 +9002,7 @@
       <c r="D48" t="n">
         <v>7</v>
       </c>
+      <c r="E48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -8971,6 +9023,7 @@
       <c r="D49" t="n">
         <v>8</v>
       </c>
+      <c r="E49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -8991,6 +9044,7 @@
       <c r="D50" t="n">
         <v>9</v>
       </c>
+      <c r="E50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -9011,6 +9065,7 @@
       <c r="D51" t="n">
         <v>10</v>
       </c>
+      <c r="E51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -9031,6 +9086,7 @@
       <c r="D52" t="n">
         <v>11</v>
       </c>
+      <c r="E52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -9051,6 +9107,7 @@
       <c r="D53" t="n">
         <v>12</v>
       </c>
+      <c r="E53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -9071,6 +9128,7 @@
       <c r="D54" t="n">
         <v>13</v>
       </c>
+      <c r="E54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -9091,6 +9149,7 @@
       <c r="D55" t="n">
         <v>14</v>
       </c>
+      <c r="E55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -9111,6 +9170,7 @@
       <c r="D56" t="n">
         <v>15</v>
       </c>
+      <c r="E56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -9131,6 +9191,7 @@
       <c r="D57" t="n">
         <v>16</v>
       </c>
+      <c r="E57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -9151,6 +9212,7 @@
       <c r="D58" t="n">
         <v>17</v>
       </c>
+      <c r="E58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -9171,6 +9233,7 @@
       <c r="D59" t="n">
         <v>18</v>
       </c>
+      <c r="E59" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dist/parameters.xlsx
+++ b/dist/parameters.xlsx
@@ -3329,12 +3329,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BV_trab_3D</t>
+          <t>TV_cort_3D</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BV</t>
+          <t>TV</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3364,12 +3364,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BVTV_trab_3D</t>
+          <t>BV_trab_3D</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BVTV</t>
+          <t>BV</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3379,7 +3379,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>um^3</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -3399,12 +3399,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TS_trab_3D</t>
+          <t>BV_cort_3D</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>TS</t>
+          <t>BV</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>um^2</t>
+          <t>um^3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -3434,12 +3434,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BS_trab_3D</t>
+          <t>BVTV_trab_3D</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BS</t>
+          <t>BVTV</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>um^2</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -3469,12 +3469,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>iS_trab_3D</t>
+          <t>BVTV_cort_3D</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>iS</t>
+          <t>BVTV</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3484,7 +3484,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>um^2</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3504,12 +3504,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BSBV_trab_3D</t>
+          <t>TS_trab_3D</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BSBV</t>
+          <t>TS</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3519,7 +3519,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1/um</t>
+          <t>um^2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3539,12 +3539,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BSTV_trab_3D</t>
+          <t>TS_cort_3D</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BSTV</t>
+          <t>TS</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3554,7 +3554,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1/um</t>
+          <t>um^2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3574,12 +3574,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TbTh_trab_3D</t>
+          <t>BS_trab_3D</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>TbTh</t>
+          <t>BS</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>um</t>
+          <t>um^2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -3609,12 +3609,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TbSp_trab_3D</t>
+          <t>BS_cort_3D</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TbSp</t>
+          <t>BS</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>um</t>
+          <t>um^2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -3644,12 +3644,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TbN_trab_3D</t>
+          <t>iS_trab_3D</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TbN</t>
+          <t>iS</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -3659,7 +3659,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1/um</t>
+          <t>um^2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -3679,12 +3679,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TbPf3D_trab_3D</t>
+          <t>iS_cort_3D</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TbPf3D</t>
+          <t>iS</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1/um</t>
+          <t>um^2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -3714,12 +3714,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CrdX3D_trab_3D</t>
+          <t>BSBV_trab_3D</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CrdX3D</t>
+          <t>BSBV</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>um</t>
+          <t>1/um</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -3749,12 +3749,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CrdY3D_trab_3D</t>
+          <t>BSBV_cort_3D</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CrdY3D</t>
+          <t>BSBV</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>um</t>
+          <t>1/um</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -3784,12 +3784,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CrdZ3D_trab_3D</t>
+          <t>BSTV_trab_3D</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CrdZ3D</t>
+          <t>BSTV</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -3799,7 +3799,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>um</t>
+          <t>1/um</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -3819,12 +3819,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SMI_trab_3D</t>
+          <t>BSTV_cort_3D</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SMI</t>
+          <t>BSTV</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -3832,7 +3832,11 @@
           <t>3D</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1/um</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>float</t>
@@ -3850,12 +3854,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DA_trab_3D</t>
+          <t>TbTh_trab_3D</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DA</t>
+          <t>TbTh</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -3863,7 +3867,11 @@
           <t>3D</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>um</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>float</t>
@@ -3881,12 +3889,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DA_ratio_trab_3D</t>
+          <t>TbTh_cort_3D</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DA_ratio</t>
+          <t>TbTh</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -3894,7 +3902,11 @@
           <t>3D</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>um</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>float</t>
@@ -3912,12 +3924,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>FD3D_trab_3D</t>
+          <t>TbSp_trab_3D</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FD3D</t>
+          <t>TbSp</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3925,7 +3937,11 @@
           <t>3D</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>um</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>float</t>
@@ -3943,12 +3959,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ObjN3D_trab_3D</t>
+          <t>TbSp_cort_3D</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ObjN3D</t>
+          <t>TbSp</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3956,7 +3972,11 @@
           <t>3D</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>um</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>float</t>
@@ -3974,12 +3994,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PoNcl3D_trab_3D</t>
+          <t>TbN_trab_3D</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PoNcl3D</t>
+          <t>TbN</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3987,7 +4007,11 @@
           <t>3D</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>1/um</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>float</t>
@@ -4005,12 +4029,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PoVcl_trab_3D</t>
+          <t>TbN_cort_3D</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PoVcl</t>
+          <t>TbN</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -4020,7 +4044,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>um^3</t>
+          <t>1/um</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -4040,12 +4064,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PoScl_trab_3D</t>
+          <t>TbPf3D_trab_3D</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>PoScl</t>
+          <t>TbPf3D</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -4055,7 +4079,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>um^2</t>
+          <t>1/um</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -4075,12 +4099,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PoVop_trab_3D</t>
+          <t>TbPf3D_cort_3D</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>PoVop</t>
+          <t>TbPf3D</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -4090,7 +4114,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>um^3</t>
+          <t>1/um</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -4110,12 +4134,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Po_op3D_trab_3D</t>
+          <t>CrdX3D_trab_3D</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Po_op3D</t>
+          <t>CrdX3D</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -4125,7 +4149,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>um</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -4145,12 +4169,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PoVtot_trab_3D</t>
+          <t>CrdX3D_cort_3D</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>PoVtot</t>
+          <t>CrdX3D</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4160,7 +4184,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>um^3</t>
+          <t>um</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -4180,12 +4204,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Po_cl_trab_3D</t>
+          <t>CrdY3D_trab_3D</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Po_cl</t>
+          <t>CrdY3D</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4195,7 +4219,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>um</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -4215,12 +4239,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Po_tot_trab_3D</t>
+          <t>CrdY3D_cort_3D</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Po_tot</t>
+          <t>CrdY3D</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4230,7 +4254,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>um</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -4250,12 +4274,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>EuN3D_trab_3D</t>
+          <t>CrdZ3D_trab_3D</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>EuN3D</t>
+          <t>CrdZ3D</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4263,7 +4287,11 @@
           <t>3D</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>um</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>float</t>
@@ -4281,12 +4309,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Conn_trab_3D</t>
+          <t>CrdZ3D_cort_3D</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Conn</t>
+          <t>CrdZ3D</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4294,7 +4322,11 @@
           <t>3D</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>um</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>float</t>
@@ -4312,12 +4344,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ConnDn_trab_3D</t>
+          <t>SMI_trab_3D</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ConnDn</t>
+          <t>SMI</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4325,11 +4357,7 @@
           <t>3D</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>1/um^3</t>
-        </is>
-      </c>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
           <t>float</t>
@@ -4347,12 +4375,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SDTbTh_trab_3D</t>
+          <t>SMI_cort_3D</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SDTbTh</t>
+          <t>SMI</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4360,11 +4388,7 @@
           <t>3D</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>um</t>
-        </is>
-      </c>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
           <t>float</t>
@@ -4382,12 +4406,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SDTbSp_trab_3D</t>
+          <t>DA_trab_3D</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SDTbSp</t>
+          <t>DA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4395,11 +4419,7 @@
           <t>3D</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>um</t>
-        </is>
-      </c>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
           <t>float</t>
@@ -4417,12 +4437,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MMIx3D_trab_3D</t>
+          <t>DA_cort_3D</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>MMIx3D</t>
+          <t>DA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4430,11 +4450,7 @@
           <t>3D</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>um^5</t>
-        </is>
-      </c>
+      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
           <t>float</t>
@@ -4452,12 +4468,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MMIy3D_trab_3D</t>
+          <t>DA_ratio_trab_3D</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>MMIy3D</t>
+          <t>DA_ratio</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -4465,11 +4481,7 @@
           <t>3D</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>um^5</t>
-        </is>
-      </c>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
           <t>float</t>
@@ -4487,12 +4499,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MMIz3D_trab_3D</t>
+          <t>DA_ratio_cort_3D</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>MMIz3D</t>
+          <t>DA_ratio</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -4500,11 +4512,7 @@
           <t>3D</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>um^5</t>
-        </is>
-      </c>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
           <t>float</t>
@@ -4522,12 +4530,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MMIpolar3D_trab_3D</t>
+          <t>FD3D_trab_3D</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>MMIpolar3D</t>
+          <t>FD3D</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4535,11 +4543,7 @@
           <t>3D</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>um^5</t>
-        </is>
-      </c>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
           <t>float</t>
@@ -4557,12 +4561,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>GrRx3D_trab_3D</t>
+          <t>FD3D_cort_3D</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>GrRx3D</t>
+          <t>FD3D</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -4570,11 +4574,7 @@
           <t>3D</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>um</t>
-        </is>
-      </c>
+      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
           <t>float</t>
@@ -4592,12 +4592,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>GrRy3D_trab_3D</t>
+          <t>ObjN3D_trab_3D</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>GrRy3D</t>
+          <t>ObjN3D</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -4605,11 +4605,7 @@
           <t>3D</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>um</t>
-        </is>
-      </c>
+      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
           <t>float</t>
@@ -4627,12 +4623,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>GrRz3D_trab_3D</t>
+          <t>ObjN3D_cort_3D</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>GrRz3D</t>
+          <t>ObjN3D</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -4640,11 +4636,7 @@
           <t>3D</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>um</t>
-        </is>
-      </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
           <t>float</t>
@@ -4662,12 +4654,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>GrRpolar3D_trab_3D</t>
+          <t>PoNcl3D_trab_3D</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GrRpolar3D</t>
+          <t>PoNcl3D</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -4675,11 +4667,7 @@
           <t>3D</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>um</t>
-        </is>
-      </c>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
           <t>float</t>
@@ -4697,12 +4685,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PrInxy3D_trab_3D</t>
+          <t>PoNcl3D_cort_3D</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>PrInxy3D</t>
+          <t>PoNcl3D</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -4710,11 +4698,7 @@
           <t>3D</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>um^5</t>
-        </is>
-      </c>
+      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
           <t>float</t>
@@ -4732,12 +4716,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PrInxz3D_trab_3D</t>
+          <t>PoVcl_trab_3D</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>PrInxz3D</t>
+          <t>PoVcl</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -4747,7 +4731,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>um^5</t>
+          <t>um^3</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4767,12 +4751,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>PrInyz3D_trab_3D</t>
+          <t>PoVcl_cort_3D</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>PrInyz3D</t>
+          <t>PoVcl</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -4782,7 +4766,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>um^5</t>
+          <t>um^3</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4802,12 +4786,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>TV_cort_3D</t>
+          <t>PoScl_trab_3D</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>TV</t>
+          <t>PoScl</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -4817,7 +4801,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>um^3</t>
+          <t>um^2</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4837,12 +4821,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BV_cort_3D</t>
+          <t>PoScl_cort_3D</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BV</t>
+          <t>PoScl</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -4852,7 +4836,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>um^3</t>
+          <t>um^2</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4872,12 +4856,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BVTV_cort_3D</t>
+          <t>PoVop_trab_3D</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BVTV</t>
+          <t>PoVop</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -4887,7 +4871,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>um^3</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -4907,12 +4891,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>TS_cort_3D</t>
+          <t>PoVop_cort_3D</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>TS</t>
+          <t>PoVop</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -4922,7 +4906,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>um^2</t>
+          <t>um^3</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -4942,12 +4926,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>BS_cort_3D</t>
+          <t>Po_op3D_trab_3D</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BS</t>
+          <t>Po_op3D</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -4957,7 +4941,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>um^2</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -4977,12 +4961,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>iS_cort_3D</t>
+          <t>Po_op3D_cort_3D</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>iS</t>
+          <t>Po_op3D</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4992,7 +4976,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>um^2</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -5012,12 +4996,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BSBV_cort_3D</t>
+          <t>PoVtot_trab_3D</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BSBV</t>
+          <t>PoVtot</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -5027,7 +5011,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>1/um</t>
+          <t>um^3</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -5047,12 +5031,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>BSTV_cort_3D</t>
+          <t>PoVtot_cort_3D</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>BSTV</t>
+          <t>PoVtot</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -5062,7 +5046,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>1/um</t>
+          <t>um^3</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -5082,12 +5066,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>TbTh_cort_3D</t>
+          <t>Po_cl_trab_3D</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>TbTh</t>
+          <t>Po_cl</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -5097,7 +5081,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>um</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5117,12 +5101,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>TbSp_cort_3D</t>
+          <t>Po_cl_cort_3D</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>TbSp</t>
+          <t>Po_cl</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -5132,7 +5116,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>um</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5152,12 +5136,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>TbN_cort_3D</t>
+          <t>Po_tot_trab_3D</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>TbN</t>
+          <t>Po_tot</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -5167,7 +5151,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>1/um</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5187,12 +5171,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>TbPf3D_cort_3D</t>
+          <t>Po_tot_cort_3D</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>TbPf3D</t>
+          <t>Po_tot</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -5202,7 +5186,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>1/um</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5222,12 +5206,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CrdX3D_cort_3D</t>
+          <t>EuN3D_trab_3D</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CrdX3D</t>
+          <t>EuN3D</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -5235,11 +5219,7 @@
           <t>3D</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>um</t>
-        </is>
-      </c>
+      <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
           <t>float</t>
@@ -5257,12 +5237,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CrdY3D_cort_3D</t>
+          <t>EuN3D_cort_3D</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CrdY3D</t>
+          <t>EuN3D</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -5270,11 +5250,7 @@
           <t>3D</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>um</t>
-        </is>
-      </c>
+      <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
           <t>float</t>
@@ -5292,12 +5268,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>CrdZ3D_cort_3D</t>
+          <t>Conn_trab_3D</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CrdZ3D</t>
+          <t>Conn</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -5305,11 +5281,7 @@
           <t>3D</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>um</t>
-        </is>
-      </c>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
           <t>float</t>
@@ -5327,12 +5299,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SMI_cort_3D</t>
+          <t>Conn_cort_3D</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SMI</t>
+          <t>Conn</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -5358,12 +5330,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>DA_cort_3D</t>
+          <t>ConnDn_trab_3D</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>DA</t>
+          <t>ConnDn</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -5371,7 +5343,11 @@
           <t>3D</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>1/um^3</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
           <t>float</t>
@@ -5389,12 +5365,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>DA_ratio_cort_3D</t>
+          <t>ConnDn_cort_3D</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>DA_ratio</t>
+          <t>ConnDn</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -5402,7 +5378,11 @@
           <t>3D</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>1/um^3</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>float</t>
@@ -5420,12 +5400,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>FD3D_cort_3D</t>
+          <t>SDTbTh_trab_3D</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>FD3D</t>
+          <t>SDTbTh</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -5433,7 +5413,11 @@
           <t>3D</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>um</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>float</t>
@@ -5451,12 +5435,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ObjN3D_cort_3D</t>
+          <t>SDTbTh_cort_3D</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ObjN3D</t>
+          <t>SDTbTh</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -5464,7 +5448,11 @@
           <t>3D</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>um</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>float</t>
@@ -5482,12 +5470,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>PoNcl3D_cort_3D</t>
+          <t>SDTbSp_trab_3D</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PoNcl3D</t>
+          <t>SDTbSp</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -5495,7 +5483,11 @@
           <t>3D</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>um</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>float</t>
@@ -5513,12 +5505,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>PoVcl_cort_3D</t>
+          <t>SDTbSp_cort_3D</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>PoVcl</t>
+          <t>SDTbSp</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -5528,7 +5520,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>um^3</t>
+          <t>um</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -5548,12 +5540,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>PoScl_cort_3D</t>
+          <t>MMIx3D_trab_3D</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PoScl</t>
+          <t>MMIx3D</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5563,7 +5555,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>um^2</t>
+          <t>um^5</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -5583,12 +5575,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>PoVop_cort_3D</t>
+          <t>MMIx3D_cort_3D</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PoVop</t>
+          <t>MMIx3D</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -5598,7 +5590,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>um^3</t>
+          <t>um^5</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -5618,12 +5610,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Po_op3D_cort_3D</t>
+          <t>MMIy3D_trab_3D</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Po_op3D</t>
+          <t>MMIy3D</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -5633,7 +5625,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>um^5</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -5653,12 +5645,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>PoVtot_cort_3D</t>
+          <t>MMIy3D_cort_3D</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>PoVtot</t>
+          <t>MMIy3D</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -5668,7 +5660,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>um^3</t>
+          <t>um^5</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -5688,12 +5680,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Po_cl_cort_3D</t>
+          <t>MMIz3D_trab_3D</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Po_cl</t>
+          <t>MMIz3D</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -5703,7 +5695,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>um^5</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -5723,12 +5715,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Po_tot_cort_3D</t>
+          <t>MMIz3D_cort_3D</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Po_tot</t>
+          <t>MMIz3D</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5738,7 +5730,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>um^5</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -5758,12 +5750,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>EuN3D_cort_3D</t>
+          <t>MMIpolar3D_trab_3D</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>EuN3D</t>
+          <t>MMIpolar3D</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5771,7 +5763,11 @@
           <t>3D</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>um^5</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>float</t>
@@ -5789,12 +5785,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Conn_cort_3D</t>
+          <t>MMIpolar3D_cort_3D</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Conn</t>
+          <t>MMIpolar3D</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5802,7 +5798,11 @@
           <t>3D</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>um^5</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>float</t>
@@ -5820,12 +5820,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ConnDn_cort_3D</t>
+          <t>GrRx3D_trab_3D</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ConnDn</t>
+          <t>GrRx3D</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5835,7 +5835,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>1/um^3</t>
+          <t>um</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5855,12 +5855,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>SDTbTh_cort_3D</t>
+          <t>GrRx3D_cort_3D</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SDTbTh</t>
+          <t>GrRx3D</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5890,12 +5890,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>SDTbSp_cort_3D</t>
+          <t>GrRy3D_trab_3D</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SDTbSp</t>
+          <t>GrRy3D</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5925,12 +5925,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>MMIx3D_cort_3D</t>
+          <t>GrRy3D_cort_3D</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>MMIx3D</t>
+          <t>GrRy3D</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5940,7 +5940,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>um^5</t>
+          <t>um</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5960,12 +5960,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>MMIy3D_cort_3D</t>
+          <t>GrRz3D_trab_3D</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>MMIy3D</t>
+          <t>GrRz3D</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5975,7 +5975,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>um^5</t>
+          <t>um</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5995,12 +5995,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>MMIz3D_cort_3D</t>
+          <t>GrRz3D_cort_3D</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>MMIz3D</t>
+          <t>GrRz3D</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -6010,7 +6010,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>um^5</t>
+          <t>um</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -6030,12 +6030,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>MMIpolar3D_cort_3D</t>
+          <t>GrRpolar3D_trab_3D</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>MMIpolar3D</t>
+          <t>GrRpolar3D</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -6045,7 +6045,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>um^5</t>
+          <t>um</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -6065,12 +6065,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>GrRx3D_cort_3D</t>
+          <t>GrRpolar3D_cort_3D</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>GrRx3D</t>
+          <t>GrRpolar3D</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -6100,12 +6100,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>GrRy3D_cort_3D</t>
+          <t>PrInxy3D_trab_3D</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>GrRy3D</t>
+          <t>PrInxy3D</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -6115,7 +6115,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>um</t>
+          <t>um^5</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -6135,12 +6135,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>GrRz3D_cort_3D</t>
+          <t>PrInxy3D_cort_3D</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>GrRz3D</t>
+          <t>PrInxy3D</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>um</t>
+          <t>um^5</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -6170,12 +6170,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>GrRpolar3D_cort_3D</t>
+          <t>PrInxz3D_trab_3D</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>GrRpolar3D</t>
+          <t>PrInxz3D</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -6185,7 +6185,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>um</t>
+          <t>um^5</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -6205,12 +6205,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>PrInxy3D_cort_3D</t>
+          <t>PrInxz3D_cort_3D</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>PrInxy3D</t>
+          <t>PrInxz3D</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -6240,12 +6240,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>PrInxz3D_cort_3D</t>
+          <t>PrInyz3D_trab_3D</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>PrInxz3D</t>
+          <t>PrInyz3D</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -8482,7 +8482,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>通用模板（同一样品CSV内多ROI分析结果）</t>
+          <t>通用模板（一个样品CSV内多个ROI分析结果）</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -8503,7 +8503,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>通用模板（同一样品CSV内多ROI分析结果）</t>
+          <t>通用模板（一个样品CSV内多个ROI分析结果）</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -8524,7 +8524,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>通用模板（同一样品CSV内多ROI分析结果）</t>
+          <t>通用模板（一个样品CSV内多个ROI分析结果）</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -8545,7 +8545,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>通用模板（同一样品CSV内多ROI分析结果）</t>
+          <t>通用模板（一个样品CSV内多个ROI分析结果）</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -8566,7 +8566,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>通用模板（同一样品CSV内多ROI分析结果）</t>
+          <t>通用模板（一个样品CSV内多个ROI分析结果）</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -8587,7 +8587,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>通用模板（同一样品CSV内多ROI分析结果）</t>
+          <t>通用模板（一个样品CSV内多个ROI分析结果）</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -8608,7 +8608,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>通用模板（同一样品CSV内多ROI分析结果）</t>
+          <t>通用模板（一个样品CSV内多个ROI分析结果）</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -8629,7 +8629,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>通用模板（同一样品CSV内多ROI分析结果）</t>
+          <t>通用模板（一个样品CSV内多个ROI分析结果）</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -8650,7 +8650,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>通用模板（同一样品CSV内多ROI分析结果）</t>
+          <t>通用模板（一个样品CSV内多个ROI分析结果）</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -8671,7 +8671,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>通用模板（同一样品CSV内多ROI分析结果）</t>
+          <t>通用模板（一个样品CSV内多个ROI分析结果）</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -8692,7 +8692,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>通用模板（同一样品CSV内多ROI分析结果）</t>
+          <t>通用模板（一个样品CSV内多个ROI分析结果）</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -8713,7 +8713,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>通用模板（同一样品CSV内多ROI分析结果）</t>
+          <t>通用模板（一个样品CSV内多个ROI分析结果）</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -8734,7 +8734,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>通用模板（同一样品CSV内多ROI分析结果）</t>
+          <t>通用模板（一个样品CSV内多个ROI分析结果）</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -8755,7 +8755,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>通用模板（同一样品CSV内多ROI分析结果）</t>
+          <t>通用模板（一个样品CSV内多个ROI分析结果）</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -8776,7 +8776,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>通用模板（同一样品CSV内多ROI分析结果）</t>
+          <t>通用模板（一个样品CSV内多个ROI分析结果）</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -8797,7 +8797,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>通用模板（同一样品CSV内多ROI分析结果）</t>
+          <t>通用模板（一个样品CSV内多个ROI分析结果）</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -8818,7 +8818,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>通用模板（同一样品CSV内多ROI分析结果）</t>
+          <t>通用模板（一个样品CSV内多个ROI分析结果）</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -8839,7 +8839,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>通用模板（同一样品CSV内多ROI分析结果）</t>
+          <t>通用模板（一个样品CSV内多个ROI分析结果）</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -8860,7 +8860,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>通用模板（同一样品不同VOI数据结果）</t>
+          <t>通用模板（一组样品不同部位、重复同名CSV）</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -8881,7 +8881,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>通用模板（同一样品不同VOI数据结果）</t>
+          <t>通用模板（一组样品不同部位、重复同名CSV）</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -8902,7 +8902,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>通用模板（同一样品不同VOI数据结果）</t>
+          <t>通用模板（一组样品不同部位、重复同名CSV）</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -8923,7 +8923,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>通用模板（同一样品不同VOI数据结果）</t>
+          <t>通用模板（一组样品不同部位、重复同名CSV）</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -8944,7 +8944,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>通用模板（同一样品不同VOI数据结果）</t>
+          <t>通用模板（一组样品不同部位、重复同名CSV）</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -8965,7 +8965,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>通用模板（同一样品不同VOI数据结果）</t>
+          <t>通用模板（一组样品不同部位、重复同名CSV）</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -8986,7 +8986,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>通用模板（同一样品不同VOI数据结果）</t>
+          <t>通用模板（一组样品不同部位、重复同名CSV）</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -9007,7 +9007,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>通用模板（同一样品不同VOI数据结果）</t>
+          <t>通用模板（一组样品不同部位、重复同名CSV）</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -9028,7 +9028,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>通用模板（同一样品不同VOI数据结果）</t>
+          <t>通用模板（一组样品不同部位、重复同名CSV）</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -9049,7 +9049,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>通用模板（同一样品不同VOI数据结果）</t>
+          <t>通用模板（一组样品不同部位、重复同名CSV）</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -9070,7 +9070,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>通用模板（同一样品不同VOI数据结果）</t>
+          <t>通用模板（一组样品不同部位、重复同名CSV）</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -9091,7 +9091,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>通用模板（同一样品不同VOI数据结果）</t>
+          <t>通用模板（一组样品不同部位、重复同名CSV）</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -9112,7 +9112,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>通用模板（同一样品不同VOI数据结果）</t>
+          <t>通用模板（一组样品不同部位、重复同名CSV）</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -9133,7 +9133,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>通用模板（同一样品不同VOI数据结果）</t>
+          <t>通用模板（一组样品不同部位、重复同名CSV）</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -9154,7 +9154,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>通用模板（同一样品不同VOI数据结果）</t>
+          <t>通用模板（一组样品不同部位、重复同名CSV）</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -9175,7 +9175,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>通用模板（同一样品不同VOI数据结果）</t>
+          <t>通用模板（一组样品不同部位、重复同名CSV）</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -9196,7 +9196,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>通用模板（同一样品不同VOI数据结果）</t>
+          <t>通用模板（一组样品不同部位、重复同名CSV）</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -9217,7 +9217,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>通用模板（同一样品不同VOI数据结果）</t>
+          <t>通用模板（一组样品不同部位、重复同名CSV）</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">

--- a/dist/parameters.xlsx
+++ b/dist/parameters.xlsx
@@ -13,6 +13,7 @@
     <sheet name="TemplateDef" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="PathRules" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="GrayUnitConfig" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Version" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -8876,7 +8877,11 @@
       <c r="D42" t="n">
         <v>1</v>
       </c>
-      <c r="E42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>{file_prefix}</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -9338,4 +9343,32 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>版本</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>